--- a/Tarihsel_Analiz_Test/ÇILGIN SAYISAL.xlsx
+++ b/Tarihsel_Analiz_Test/ÇILGIN SAYISAL.xlsx
@@ -1133,7 +1133,7 @@
         <v>31</v>
       </c>
       <c r="I8" s="4">
-        <v>46191</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
